--- a/input/reg_health_mental.xlsx
+++ b/input/reg_health_mental.xlsx
@@ -1,33 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\InitialPopulationCreation\regression_estimates\results\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D5EF05E-435D-4B11-98A2-7BEA45FC7279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Info" sheetId="1" r:id="rId1"/>
-    <sheet name="Gof" sheetId="2" r:id="rId2"/>
-    <sheet name="HM1_L" sheetId="3" r:id="rId3"/>
-    <sheet name="HM2_Females_L" sheetId="4" r:id="rId4"/>
-    <sheet name="HM2_Males_L" sheetId="5" r:id="rId5"/>
-    <sheet name="HM1_C" sheetId="6" r:id="rId6"/>
-    <sheet name="HM2_Females_C" sheetId="7" r:id="rId7"/>
-    <sheet name="HM2_Males_C" sheetId="8" r:id="rId8"/>
+    <sheet name="Info" sheetId="1" r:id="rId2"/>
+    <sheet name="Gof" sheetId="2" r:id="rId4"/>
+    <sheet name="HM1_L" sheetId="3" r:id="rId5"/>
+    <sheet name="HM2_Females_L" sheetId="4" r:id="rId6"/>
+    <sheet name="HM2_Males_L" sheetId="5" r:id="rId7"/>
+    <sheet name="HM1_C" sheetId="6" r:id="rId8"/>
+    <sheet name="HM2_Females_C" sheetId="7" r:id="rId9"/>
+    <sheet name="HM2_Males_C" sheetId="8" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="0" fullCalcOnLoad="true"/>
+  <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="847" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="294" uniqueCount="89">
   <si>
     <t>Description:</t>
   </si>
@@ -197,6 +190,9 @@
     <t>N</t>
   </si>
   <si>
+    <t>VARIANCE</t>
+  </si>
+  <si>
     <t>PersistentEmployed</t>
   </si>
   <si>
@@ -228,18 +224,6 @@
   </si>
   <si>
     <t>D_Econ_benefits_UC</t>
-  </si>
-  <si>
-    <t>D_Econ_benefits_UC_Lhw_TEN</t>
-  </si>
-  <si>
-    <t>D_Econ_benefits_UC_Lhw_TWENTY</t>
-  </si>
-  <si>
-    <t>D_Econ_benefits_UC_Lhw_THIRTY</t>
-  </si>
-  <si>
-    <t>D_Econ_benefits_UC_Lhw_FORTY</t>
   </si>
   <si>
     <t>HM2_Females_L: GHQ score 0-36</t>
@@ -304,274 +288,105 @@
   <si>
     <t>HM2_Males_C: GHQ score 0-12</t>
   </si>
-  <si>
-    <t>EmployedToUnemployed</t>
-  </si>
-  <si>
-    <t>NonPovertyToPoverty</t>
-  </si>
-  <si>
-    <t>VARIANCE</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="51">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
       <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <b/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -582,77 +397,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="31">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -730,169 +475,49 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
-    <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="16" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="17" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="18" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="19" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="20" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="21" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="23" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="24" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="25" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="26" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="27" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="28" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="29" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="30" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -900,348 +525,23 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="true">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="true">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
-              <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill rotWithShape="true">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="false"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1249,20 +549,20 @@
         <v>3</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1270,7 +570,7 @@
         <v>7</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1278,7 +578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1286,7 +586,7 @@
         <v>11</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -1294,7 +594,7 @@
         <v>13</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1302,7 +602,7 @@
         <v>15</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -1311,26 +611,25 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F25"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+    <row r="1">
+      <c r="A1" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" s="25" t="s">
+    <row r="3">
+      <c r="A3" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>54</v>
       </c>
@@ -1338,7 +637,7 @@
         <v>0.3201831881181405</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -1346,20 +645,20 @@
         <v>217589</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>54</v>
       </c>
       <c r="B8">
-        <v>0.58981592966182261</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+        <v>0.58941712803372326</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>55</v>
       </c>
@@ -1367,20 +666,20 @@
         <v>98541</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="11">
+      <c r="A11" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
         <v>54</v>
       </c>
       <c r="B12">
-        <v>0.5925105739771992</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+        <v>0.5921300480115258</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>55</v>
       </c>
@@ -1388,26 +687,26 @@
         <v>83407</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" s="28" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="15">
+      <c r="A15" s="8" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B16">
         <v>0.07294910586204606</v>
       </c>
       <c r="E16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F16">
         <v>19701.58044008445</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>55</v>
       </c>
@@ -1415,26 +714,26 @@
         <v>192054</v>
       </c>
       <c r="E17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F17">
         <v>-221628158.87748379</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="19">
+      <c r="A19" s="9" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>54</v>
       </c>
       <c r="B20">
-        <v>0.53501993544745818</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+        <v>0.53468306966561807</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1442,20 +741,20 @@
         <v>98541</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="23">
+      <c r="A23" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>54</v>
       </c>
       <c r="B24">
-        <v>0.53375399313431093</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+        <v>0.53329089154962572</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>55</v>
       </c>
@@ -1464,16 +763,15 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AH33"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -1577,7 +875,7 @@
         <v>52</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -1681,7 +979,7 @@
         <v>-0.0080793628703861604</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -1785,7 +1083,7 @@
         <v>-0.00076383513831104115</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -1889,7 +1187,7 @@
         <v>-0.0015745492370541608</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -1993,7 +1291,7 @@
         <v>1.7256128473918758e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -2097,7 +1395,7 @@
         <v>-0.00021736012663203458</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -2201,7 +1499,7 @@
         <v>-0.00025916428257782831</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -2305,7 +1603,7 @@
         <v>-0.0013817755793306258</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -2409,7 +1707,7 @@
         <v>-0.0019672435428968954</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -2513,7 +1811,7 @@
         <v>-0.00042377350365329454</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -2617,7 +1915,7 @@
         <v>-0.0025874419510391669</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -2721,7 +2019,7 @@
         <v>0.00060525479934199619</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -2825,7 +2123,7 @@
         <v>-0.0027602788887804313</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -2929,7 +2227,7 @@
         <v>-0.0018652075687583217</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -3033,7 +2331,7 @@
         <v>-0.0015082783057825317</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -3137,7 +2435,7 @@
         <v>-0.001111208170744078</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -3241,7 +2539,7 @@
         <v>-0.002159983547061527</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -3345,7 +2643,7 @@
         <v>-0.0034749237363621592</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -3449,7 +2747,7 @@
         <v>-0.003192805182633084</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -3553,7 +2851,7 @@
         <v>-0.0032900723150382791</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -3657,7 +2955,7 @@
         <v>-0.0027090746766821796</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -3761,7 +3059,7 @@
         <v>-0.0033725954891818777</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -3865,7 +3163,7 @@
         <v>-0.0035989498819954755</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -3969,7 +3267,7 @@
         <v>-0.0027697742019989818</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -4073,7 +3371,7 @@
         <v>-0.0030186114303124918</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -4177,7 +3475,7 @@
         <v>-0.0044213484095247686</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -4281,7 +3579,7 @@
         <v>-0.0030149383199262205</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -4385,7 +3683,7 @@
         <v>-0.0031238428641618384</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -4489,7 +3787,7 @@
         <v>-0.00022712363506476572</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -4593,7 +3891,7 @@
         <v>-0.0019060188066832844</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -4697,7 +3995,7 @@
         <v>-0.002166023166306888</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -4801,7 +4099,7 @@
         <v>-0.0035225851034430505</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
         <v>52</v>
       </c>
@@ -4906,16 +4204,15 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -4923,587 +4220,455 @@
         <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>-0.48132628732264948</v>
+      </c>
+      <c r="C2">
+        <v>0.014050119566589723</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>-1.1423822347141468</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.024389742263859777</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>-0.2703561225543738</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.0151739604996039</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>-0.038913813761901998</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.010013711902745729</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>61</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>-0.029781316599001292</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.014499018479142934</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>62</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>0.065003304383723273</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.016638473568664019</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>63</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>0.074300516443436451</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.0018186634254726602</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>64</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>-0.020320845363848615</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.0019554044092952344</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>65</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>2.6868618242593017</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.01151972801735762</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>66</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>0.1126961809370413</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.0041265606131392126</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>67</v>
       </c>
-      <c r="O1" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2">
-        <v>-0.12733619911499125</v>
-      </c>
-      <c r="C2">
-        <v>0.044247871719342059</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3">
-        <v>-0.75613500057645777</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.052994840732581837</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4">
-        <v>-0.32659946383081207</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.015274976014226666</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5">
-        <v>-0.044335882884527562</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.0099901805755577052</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6">
-        <v>-0.028483196493539201</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.014512383411249354</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7">
-        <v>0.058882507395374283</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.016538956977328993</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8">
-        <v>0.077779730914549164</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.0018227731942310624</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9">
-        <v>-0.026731905864342639</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.0019698782310888785</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10">
-        <v>2.6887734325300605</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.011493191485708813</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11">
-        <v>0.13844411433427006</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.0041262715766742144</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>66</v>
-      </c>
       <c r="B12">
-        <v>1.2042857951056947</v>
+        <v>0.81541887113636757</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -5536,244 +4701,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.070954094299055748</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13">
-        <v>0.056438970360966553</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0.43392072508742974</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14">
-        <v>-0.55642081907942342</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.16212624054801716</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15">
-        <v>-1.0460269790408237</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0.23607110930474298</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16">
-        <v>-1.0096838611300114</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.16727796239540116</v>
+        <v>0.033092249311941054</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -5781,587 +4721,455 @@
         <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>-0.74896525138542469</v>
+      </c>
+      <c r="C2">
+        <v>0.023066368206263899</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>-1.1329218123615816</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.044969993747266401</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>-0.27250518305004257</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.034150770723028703</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>-0.23211439379688159</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.012630913546465932</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>61</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>-0.24220135883226374</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.017723136149317368</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>62</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>-0.15393293372640238</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.022636651171750528</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>63</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>0.049212120349033606</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.0015812616031843166</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>64</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>0.03150885967656443</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.0017355655034191847</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>65</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>2.6657733854692527</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.015022112095149746</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>66</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>0.088268660311672173</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.0046289170723851376</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>67</v>
       </c>
-      <c r="O1" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2">
-        <v>0.32083976890764493</v>
-      </c>
-      <c r="C2">
-        <v>0.10804510216443207</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3">
-        <v>-0.047442641623228289</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.12545167540681904</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4">
-        <v>-0.34109385796011893</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.033786602699084033</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5">
-        <v>-0.22592224177750281</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.012548799012465027</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6">
-        <v>-0.23538970335260667</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.017681359678117719</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7">
-        <v>-0.15217520107485402</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.022586968426389655</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8">
-        <v>0.048415549090163212</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.0015747926205129518</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9">
-        <v>0.03711562135148197</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.0016960695012924745</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10">
-        <v>2.6593242177235075</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.014994187541755678</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11">
-        <v>0.088750076298848582</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.0046360878971249348</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>66</v>
-      </c>
       <c r="B12">
-        <v>0.93895916434076576</v>
+        <v>0.65477144503704854</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -6394,244 +5202,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.14049822369002568</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13">
-        <v>0.99351951985089893</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>1.234266969966195</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14">
-        <v>-1.4780985384686012</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.40548780715305538</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15">
-        <v>-0.30755464848583836</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0.66388722712180337</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16">
-        <v>-0.47733090738632056</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.17937940064964097</v>
+        <v>0.054176061317035722</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AS44"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -6651,7 +5234,7 @@
         <v>24</v>
       </c>
       <c r="G1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="H1" t="s">
         <v>26</v>
@@ -6732,43 +5315,43 @@
         <v>51</v>
       </c>
       <c r="AH1" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AK1" t="s">
         <v>74</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AL1" t="s">
         <v>75</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AM1" t="s">
         <v>76</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AN1" t="s">
         <v>77</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AO1" t="s">
         <v>78</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AP1" t="s">
         <v>79</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AQ1" t="s">
         <v>80</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AR1" t="s">
         <v>81</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AS1" t="s">
         <v>82</v>
       </c>
-      <c r="AQ1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>84</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2">
       <c r="A2" t="s">
         <v>21</v>
       </c>
@@ -6905,7 +5488,7 @@
         <v>0.0013833644319047732</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -7042,7 +5625,7 @@
         <v>0.00010518589345343647</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -7179,7 +5762,7 @@
         <v>0.00051276531159404678</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -7316,9 +5899,9 @@
         <v>-5.4818719527368262e-06</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B6">
         <v>0.26331411575135483</v>
@@ -7453,7 +6036,7 @@
         <v>3.7017970043510743e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -7590,7 +6173,7 @@
         <v>2.7799674853697721e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -7727,7 +6310,7 @@
         <v>5.2544465755339926e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -7864,7 +6447,7 @@
         <v>9.7040391630571417e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -8001,7 +6584,7 @@
         <v>-5.9971344923956149e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -8138,7 +6721,7 @@
         <v>0.00026215836060695724</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -8275,7 +6858,7 @@
         <v>-0.00010258905689099783</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -8412,7 +6995,7 @@
         <v>0.00052302605054409918</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -8549,7 +7132,7 @@
         <v>0.00042960728680945583</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -8686,7 +7269,7 @@
         <v>0.0003789608264707328</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" t="s">
         <v>35</v>
       </c>
@@ -8823,7 +7406,7 @@
         <v>0.00024190784546232561</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="17" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -8960,7 +7543,7 @@
         <v>0.00029218012872086021</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="18" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -9097,7 +7680,7 @@
         <v>0.00046327835749601914</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="19" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -9234,7 +7817,7 @@
         <v>0.00046675143193423616</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="20" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -9371,7 +7954,7 @@
         <v>0.00040876358807502658</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="21" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" t="s">
         <v>40</v>
       </c>
@@ -9508,7 +8091,7 @@
         <v>0.00040360357960106527</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="22" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -9645,7 +8228,7 @@
         <v>0.00039532588643519703</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="23" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" t="s">
         <v>42</v>
       </c>
@@ -9782,7 +8365,7 @@
         <v>0.00048687382928946758</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="24" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" t="s">
         <v>43</v>
       </c>
@@ -9919,7 +8502,7 @@
         <v>0.0003459783217011625</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="25" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" t="s">
         <v>44</v>
       </c>
@@ -10056,7 +8639,7 @@
         <v>0.00044379178099409255</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="26" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" t="s">
         <v>45</v>
       </c>
@@ -10193,7 +8776,7 @@
         <v>0.00055809265051142191</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="27" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -10330,7 +8913,7 @@
         <v>0.00042269482336051707</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="28" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -10467,7 +9050,7 @@
         <v>0.00040596369356806633</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="29" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" t="s">
         <v>48</v>
       </c>
@@ -10604,7 +9187,7 @@
         <v>4.4115402496559906e-05</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="30" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" t="s">
         <v>49</v>
       </c>
@@ -10741,7 +9324,7 @@
         <v>0.00020504612054208447</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="31" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" t="s">
         <v>50</v>
       </c>
@@ -10878,7 +9461,7 @@
         <v>0.00024923542387982078</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="32" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -11015,9 +9598,9 @@
         <v>0.00025708840265188258</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="33" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B33">
         <v>-1.0119574286768098</v>
@@ -11152,9 +9735,9 @@
         <v>0.014296206160676582</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="34" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B34">
         <v>-0.20577061878924133</v>
@@ -11289,9 +9872,9 @@
         <v>0.014287898701916468</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="35" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B35">
         <v>0.26756482390157937</v>
@@ -11426,9 +10009,9 @@
         <v>0.0142860069989455</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="36" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B36">
         <v>0.57321243689614465</v>
@@ -11563,9 +10146,9 @@
         <v>0.014297186803161853</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="37" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B37">
         <v>0.84999294058233543</v>
@@ -11700,9 +10283,9 @@
         <v>0.014318187969738851</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="38" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B38">
         <v>1.1096798486452386</v>
@@ -11837,9 +10420,9 @@
         <v>0.014332102344506804</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="39" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B39">
         <v>1.3730706257588268</v>
@@ -11974,9 +10557,9 @@
         <v>0.014353304833938058</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="40" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B40">
         <v>1.6430368927097618</v>
@@ -12111,9 +10694,9 @@
         <v>0.014391363077978968</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="41" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B41">
         <v>1.9255385386699939</v>
@@ -12248,9 +10831,9 @@
         <v>0.014439190719769625</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="42" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B42">
         <v>2.2601341881709369</v>
@@ -12385,9 +10968,9 @@
         <v>0.014511502914638657</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="43" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B43">
         <v>2.678112499190414</v>
@@ -12522,9 +11105,9 @@
         <v>0.014617272610686146</v>
       </c>
     </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="44" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B44">
         <v>3.353709225999018</v>
@@ -12660,16 +11243,15 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -12677,587 +11259,455 @@
         <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>-0.381996095084223</v>
+      </c>
+      <c r="C2">
+        <v>0.0045923766193276339</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>-0.68842224862566059</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.0082724891853357321</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>-0.27037968520400313</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.0052191827598760737</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>-0.039900533252726807</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.0037461831750704969</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>61</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>-0.015541351174691962</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.0053613773585551297</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>62</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>0.04039172209279239</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.0060351488934874183</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>63</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>0.023143077415376839</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.00065900222871098472</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>64</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>-0.037505029873682622</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.00072937815252621175</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>65</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>1.4546241851606112</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.0038721225182241723</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>66</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>0.075812270326456918</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.0014646310924041697</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>67</v>
       </c>
-      <c r="O1" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2">
-        <v>-0.2557002194127071</v>
-      </c>
-      <c r="C2">
-        <v>0.015918774689746822</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3">
-        <v>-0.54221766773301749</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.019462110090069547</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4">
-        <v>-0.29655067991656126</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.0052570353635429902</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5">
-        <v>-0.043355899089929359</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.0037422123301018508</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6">
-        <v>-0.015206393735769652</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.0053549309339615842</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7">
-        <v>0.037216458241135696</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.0059943390567489948</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8">
-        <v>0.024871709052339853</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.00065965138931055962</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9">
-        <v>-0.041515752268812905</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.00073532728363911548</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10">
-        <v>1.4557067161654709</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.0038720252886793242</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11">
-        <v>0.090056359168079386</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.0014668880275660752</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>66</v>
-      </c>
       <c r="B12">
-        <v>0.66530337463024336</v>
+        <v>0.43993672221233582</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -13290,244 +11740,19 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.025597064523896537</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13">
-        <v>-0.070622956049872065</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0.14776113136910687</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14">
-        <v>-0.23510266529571078</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.060052228794545658</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15">
-        <v>-0.70848500962943617</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0.09646029247409843</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16">
-        <v>-0.57360109101993473</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.060977109945117611</v>
+        <v>0.011598008511988521</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -13535,587 +11760,455 @@
         <v>20</v>
       </c>
       <c r="C1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" t="s">
+        <v>63</v>
+      </c>
+      <c r="J1" t="s">
+        <v>64</v>
+      </c>
+      <c r="K1" t="s">
+        <v>65</v>
+      </c>
+      <c r="L1" t="s">
+        <v>66</v>
+      </c>
+      <c r="M1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
         <v>57</v>
       </c>
-      <c r="E1" t="s">
+      <c r="B2">
+        <v>-0.54913718844472337</v>
+      </c>
+      <c r="C2">
+        <v>0.0071108757514919737</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
         <v>58</v>
       </c>
-      <c r="F1" t="s">
+      <c r="B3">
+        <v>-0.63057013983121324</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0.015218601518738474</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
         <v>59</v>
       </c>
-      <c r="G1" t="s">
+      <c r="B4">
+        <v>-0.23802632872538729</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0.010504548321005279</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
         <v>60</v>
       </c>
-      <c r="H1" t="s">
+      <c r="B5">
+        <v>-0.12177762194515267</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0.0040073692145827337</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>61</v>
       </c>
-      <c r="I1" t="s">
+      <c r="B6">
+        <v>-0.093699202591708913</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.0060651933910296279</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
         <v>62</v>
       </c>
-      <c r="J1" t="s">
+      <c r="B7">
+        <v>-0.023275614737070662</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0.0077946691964566094</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
         <v>63</v>
       </c>
-      <c r="K1" t="s">
+      <c r="B8">
+        <v>0.0038765317086127604</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0.00053720435938256397</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
         <v>64</v>
       </c>
-      <c r="L1" t="s">
+      <c r="B9">
+        <v>0.00038128493765393509</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0.00056869864162784219</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
         <v>65</v>
       </c>
-      <c r="M1" t="s">
+      <c r="B10">
+        <v>1.4797329174998035</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0.0051224640830223956</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>66</v>
       </c>
-      <c r="N1" t="s">
+      <c r="B11">
+        <v>0.063249641823665909</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0.0015288245159647744</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
         <v>67</v>
       </c>
-      <c r="O1" t="s">
-        <v>68</v>
-      </c>
-      <c r="P1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2">
-        <v>0.13992676874480187</v>
-      </c>
-      <c r="C2">
-        <v>0.03281439035886842</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>0</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B3">
-        <v>0.064764750589432305</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>0.039033975677693525</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3">
-        <v>0</v>
-      </c>
-      <c r="P3">
-        <v>0</v>
-      </c>
-      <c r="Q3">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B4">
-        <v>-0.28042886957818874</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0.010427997117431967</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4">
-        <v>0</v>
-      </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
-      <c r="Q4">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B5">
-        <v>-0.11823934295627331</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5">
-        <v>0.0039884686424243232</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5">
-        <v>0</v>
-      </c>
-      <c r="P5">
-        <v>0</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6">
-        <v>-0.089790230242808244</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0.0060577354716484884</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7">
-        <v>-0.022834633866966471</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0.0077733194154961079</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8">
-        <v>0.0032610750524207782</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0.00053648646063929057</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>63</v>
-      </c>
-      <c r="B9">
-        <v>0.0044063845204308939</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0.00056401704980533574</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>64</v>
-      </c>
-      <c r="B10">
-        <v>1.4760613363769899</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>0.0051074906517341234</v>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11">
-        <v>0.062760661190522135</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0.0015267098243510662</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>66</v>
-      </c>
       <c r="B12">
-        <v>0.38871692158382154</v>
+        <v>0.29791644641775794</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -14148,234 +12241,9 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0.046023371246377717</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="13" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B13">
-        <v>0.31209888379585005</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0.36232720711394156</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B14">
-        <v>-0.88830666907720346</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0.10734560943934875</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="15" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>69</v>
-      </c>
-      <c r="B15">
-        <v>0.23484019241371956</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15">
-        <v>0</v>
-      </c>
-      <c r="P15">
-        <v>0.23870565291382378</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-    </row>
-    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16">
-        <v>-0.13616971926083468</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>0</v>
-      </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>0.06146127322301409</v>
+        <v>0.01782482340533912</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>